--- a/reports/gms_17_20260320.xlsx
+++ b/reports/gms_17_20260320.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -561,22 +561,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>53.02%</t>
+          <t>32.16%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>41.23%</t>
+          <t>28.30%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>70.15%</t>
+          <t>39.47%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -598,624 +598,639 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>⁠000558</t>
+          <t>⁠002155</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>天府文旅</t>
+          <t>湖南黄金</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-16.59%</t>
+          <t>-10.62%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-17.72%</t>
+          <t>-12.62%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-15.06%</t>
+          <t>-11.21%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>⁠000651</t>
+          <t>⁠300058</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>格力电器</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-33.60%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-38.94%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-28.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>⁠000709</t>
+          <t>⁠300750</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>河钢股份</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>413.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>371.43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>8.99%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-3.59%</t>
+          <t>9.88%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>⁠000721</t>
+          <t>⁠600307</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>西安饮食</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.36%</t>
+          <t>15.73%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-10.88%</t>
+          <t>14.55%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-9.81%</t>
+          <t>17.03%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-6.58%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>⁠000905</t>
+          <t>⁠603667</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>厦门港务</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>65.49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.03%</t>
+          <t>-27.54%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-11.22%</t>
+          <t>-31.84%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-10.09%</t>
+          <t>-24.15%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>⁠000983</t>
+          <t>⁠688291</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>山西焦煤</t>
+          <t>金橙子</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-26.22%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-31.33%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>-23.86%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>⁠002050</t>
+          <t>⁠688498</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>源杰科技</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.23</t>
+          <t>1114.99</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>345.68</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>861.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.61%</t>
+          <t>40.11%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-15.96%</t>
+          <t>31.00%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-13.77%</t>
+          <t>44.93%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>17.37%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>⁠002155</t>
+          <t>⁠000651</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>湖南黄金</t>
+          <t>格力电器</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.23%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-14.53%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-12.68%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>⁠002171</t>
+          <t>⁠600105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>楚江新材</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.60%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-14.25%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-12.47%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>⁠002230</t>
+          <t>⁠002050</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1225,48 +1240,48 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>44.23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>53.90</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.34%</t>
+          <t>-17.31%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-12.13%</t>
+          <t>-19.08%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-10.82%</t>
+          <t>-16.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1278,136 +1293,136 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>⁠002271</t>
+          <t>⁠002230</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>东方雨虹</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>53.53</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-17.65%</t>
+          <t>-16.33%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-20.34%</t>
+          <t>-17.81%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-16.90%</t>
+          <t>-15.12%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>⁠002364</t>
+          <t>⁠002271</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中恒电气</t>
+          <t>东方雨虹</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>33.94</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.33%</t>
+          <t>-18.11%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-4.85%</t>
+          <t>-20.81%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-4.62%</t>
+          <t>-17.23%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-3.99%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1439,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1434,7 +1449,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1445,22 +1460,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-8.16%</t>
+          <t>-7.98%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-8.55%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-7.88%</t>
+          <t>-7.80%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1475,243 +1490,238 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>⁠002709</t>
+          <t>⁠300139</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>晓程科技</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.80</t>
+          <t>58.85</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>67.44</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>⁠00700</t>
+          <t>⁠603583</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>捷昌驱动</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>513.00</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>528.55</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-3.59%</t>
+          <t>-17.12%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-3.70%</t>
+          <t>-18.66%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>-15.73%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-6.81%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>⁠00981</t>
+          <t>⁠688114</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>华大智造</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>51.57</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>64.78</t>
+          <t>58.32</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-15.51%</t>
+          <t>-25.02%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-16.82%</t>
+          <t>-28.29%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-14.40%</t>
+          <t>-22.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>⁠01810</t>
+          <t>⁠000905</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>小米集团－Ｗ</t>
+          <t>厦门港务</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>左侧</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1722,22 +1732,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-10.49%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-11.79%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-10.55%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1747,92 +1757,92 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>总分70.0 蓄势70.0(引力0.0+平衡40.0+量缩30.0)A 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>⁠02269</t>
+          <t>⁠002709</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>药明生物</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>42.80</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-19.28%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-21.16%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-17.46%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力40.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>⁠02565</t>
+          <t>⁠301275</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>派格生物医药－Ｂ</t>
+          <t>汉朔科技</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1842,148 +1852,148 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-18.55</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>59.61</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-18.28%</t>
+          <t>-36.61%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-19.52%</t>
+          <t>-46.78%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-16.33%</t>
+          <t>-31.87%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-5.46%</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力30.0+平衡0.0+量缩0.0) 动量20.0(推力0.0+支撑-10.0+攻击30.0)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>⁠02899</t>
+          <t>⁠000558</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>天府文旅</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>34.70</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-25.06%</t>
+          <t>-14.05%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-29.74%</t>
+          <t>-15.04%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-22.92%</t>
+          <t>-13.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-7.07%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>⁠03690</t>
+          <t>⁠000721</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>美团－Ｗ</t>
+          <t>西安饮食</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.70</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1994,22 +2004,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-5.22%</t>
+          <t>-9.83%</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-5.14%</t>
+          <t>-10.40%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-4.89%</t>
+          <t>-9.42%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2019,248 +2029,243 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>⁠03750</t>
+          <t>⁠300919</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中伟新材</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>644.00</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>116.00</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>550.76</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21.06%</t>
+          <t>-13.59%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18.01%</t>
+          <t>-15.04%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21.97%</t>
+          <t>-13.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>⁠09988</t>
+          <t>⁠600570</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>阿里巴巴－Ｗ</t>
+          <t>恒生电子</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>132.00</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-26.60</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>139.13</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-19.12%</t>
+          <t>-16.37%</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-20.15%</t>
+          <t>-17.78%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-16.77%</t>
+          <t>-15.09%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>-3.90%</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>⁠300058</t>
+          <t>⁠600966</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>博汇纸业</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-23.19%</t>
+          <t>-15.60%</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-26.39%</t>
+          <t>-18.43%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-20.88%</t>
+          <t>-15.56%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-6.13%</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>⁠300139</t>
+          <t>⁠601138</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>晓程科技</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>左侧</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>58.85</t>
+          <t>50.30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2271,22 +2276,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>67.47</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>-9.30%</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-10.00%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-9.09%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2296,311 +2301,311 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>总分70.0 蓄势70.0(引力20.0+平衡20.0+量缩30.0)A 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>⁠300223</t>
+          <t>⁠601231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>北京君正</t>
+          <t>环旭电子</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>119.80</t>
+          <t>35.82</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>125.79</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>-15.20%</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>-17.48%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>-14.88%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量50.0(推力40.0+支撑-10.0+攻击20.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>⁠300699</t>
+          <t>⁠601636</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>光威复材</t>
+          <t>旗滨集团</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H29" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-11.69%</t>
+          <t>-20.67%</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-12.96%</t>
+          <t>-23.65%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-11.48%</t>
+          <t>-19.12%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>⁠300705</t>
+          <t>⁠603933</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>九典制药</t>
+          <t>睿能科技</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-6.78%</t>
+          <t>-10.90%</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-7.03%</t>
+          <t>-11.73%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-6.57%</t>
+          <t>-10.50%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>⁠300750</t>
+          <t>⁠688981</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>413.00</t>
+          <t>102.18</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>32.50</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>369.18</t>
+          <t>109.70</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8.80%</t>
+          <t>-13.13%</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8.11%</t>
+          <t>-14.09%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8.83%</t>
+          <t>-12.35%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>⁠300919</t>
+          <t>⁠920263</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中伟新材</t>
+          <t>中航泰达</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2611,22 +2616,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-13.45%</t>
+          <t>-13.68%</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-15.07%</t>
+          <t>-15.42%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-13.09%</t>
+          <t>-13.36%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2636,641 +2641,636 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>⁠301275</t>
+          <t>⁠000709</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>汉朔科技</t>
+          <t>河钢股份</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-16.85</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>51.63</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.63%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-40.18%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-28.66%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>-5.46%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力30.0+平衡0.0+量缩0.0) 动量20.0(推力0.0+支撑-10.0+攻击30.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>⁠600105</t>
+          <t>⁠000983</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>山西焦煤</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>⁠600307</t>
+          <t>⁠002171</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>酒钢宏兴</t>
+          <t>楚江新材</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="n">
         <v>9</v>
       </c>
-      <c r="H35" t="n">
-        <v>10</v>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>22.49%</t>
+          <t>-14.98%</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19.30%</t>
+          <t>-17.16%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>23.91%</t>
+          <t>-14.65%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>总分60.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量60.0(推力0.0+支撑30.0+攻击30.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>⁠600525</t>
+          <t>⁠002364</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>中恒电气</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>33.80</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17.69%</t>
+          <t>-17.33%</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17.18%</t>
+          <t>-20.13%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20.75%</t>
+          <t>-16.76%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>⁠600570</t>
+          <t>⁠300699</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>恒生电子</t>
+          <t>光威复材</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>38.30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-12.60%</t>
+          <t>-15.43%</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-13.25%</t>
+          <t>-17.53%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-11.70%</t>
+          <t>-14.92%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-3.90%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>⁠600838</t>
+          <t>⁠600525</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>ST长园</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-6.76%</t>
+          <t>15.51%</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-6.79%</t>
+          <t>15.54%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-6.36%</t>
+          <t>18.40%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-4.22%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>⁠600966</t>
+          <t>⁠688066</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>博汇纸业</t>
+          <t>航天宏图</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" t="n">
         <v>11</v>
       </c>
-      <c r="H39" t="n">
-        <v>9</v>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-8.05%</t>
+          <t>-9.32%</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-8.99%</t>
+          <t>-10.40%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-8.25%</t>
+          <t>-9.42%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>-6.13%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>⁠601138</t>
+          <t>⁠300223</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>工业富联</t>
+          <t>北京君正</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>50.30</t>
+          <t>119.80</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>125.75</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-8.72%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-9.39%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-8.59%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>⁠601231</t>
+          <t>⁠300705</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>环旭电子</t>
+          <t>九典制药</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>41.30</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-5.74%</t>
+          <t>-9.35%</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-6.61%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-6.20%</t>
+          <t>-9.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-2.48%</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>⁠601636</t>
+          <t>⁠600838</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>旗滨集团</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3296,22 +3296,22 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-18.05%</t>
+          <t>-7.90%</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-20.42%</t>
+          <t>-8.24%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-16.96%</t>
+          <t>-7.61%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>-4.22%</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3333,420 +3333,420 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>⁠603583</t>
+          <t>⁠688256</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>捷昌驱动</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>1025.00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-87.50</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>1114.21</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-11.62%</t>
+          <t>-7.85%</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-12.47%</t>
+          <t>-8.54%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-11.09%</t>
+          <t>-7.87%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-2.28%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>⁠603667</t>
+          <t>⁠688795</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>摩尔线程</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>65.49</t>
+          <t>548.63</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-33.17</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>76.81</t>
+          <t>572.40</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-26.73%</t>
+          <t>-5.79%</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-30.68%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-23.48%</t>
+          <t>-5.70%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>⁠603933</t>
+          <t>⁠00981</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>56.90</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>64.14</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-8.92%</t>
+          <t>-20.97%</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-9.43%</t>
+          <t>-23.64%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-8.62%</t>
+          <t>-19.12%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>-4.77%</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>⁠688066</t>
+          <t>⁠02899</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>航天宏图</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H46" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-5.69%</t>
+          <t>-18.11%</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-5.97%</t>
+          <t>-21.51%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-5.63%</t>
+          <t>-17.70%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-6.62%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>⁠688114</t>
+          <t>⁠00700</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>华大智造</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>51.57</t>
+          <t>508.00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-14.52</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>527.35</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-24.57%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-27.63%</t>
+          <t>-4.92%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-21.65%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>⁠688256</t>
+          <t>⁠02269</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>药明生物</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1025.00</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-41.88</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
         <v>8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1116.91</t>
+          <t>37.07</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-16.67%</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-4.04%</t>
+          <t>-18.27%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-15.45%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>⁠688291</t>
+          <t>⁠03690</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>金橙子</t>
+          <t>美团－Ｗ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3756,48 +3756,48 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>79.16</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-11.07%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>-12.94%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-11.46%</t>
+          <t>-3.65%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3809,272 +3809,272 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>⁠688498</t>
+          <t>⁠09988</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>源杰科技</t>
+          <t>阿里巴巴－Ｗ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1114.99</t>
+          <t>123.70</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>212.40</t>
+          <t>-31.70</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>842.97</t>
+          <t>137.39</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>25.20%</t>
+          <t>-23.07%</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>22.36%</t>
+          <t>-25.63%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>28.80%</t>
+          <t>-20.40%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>17.37%</t>
+          <t>-6.29%</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>⁠688795</t>
+          <t>⁠01810</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>摩尔线程</t>
+          <t>小米集团－Ｗ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>548.63</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>573.17</t>
+          <t>34.38</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-10.59%</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>-10.96%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-9.88%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-8.59%</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>⁠688981</t>
+          <t>⁠02565</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>派格生物医药－Ｂ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>102.18</t>
+          <t>59.50</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>110.34</t>
+          <t>59.25</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-8.20%</t>
+          <t>-5.99%</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>-8.54%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-7.87%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>-3.57%</t>
+          <t>6.54%</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>⁠920263</t>
+          <t>⁠03750</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>中航泰达</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>698.00</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>180.50</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>559.26</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-16.60%</t>
+          <t>32.27%</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-19.33%</t>
+          <t>25.86%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-16.20%</t>
+          <t>34.88%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>8.39%</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
